--- a/docs/work_plan.xlsx
+++ b/docs/work_plan.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -822,18 +822,18 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>UI + now persists local session and creates backend patrol at start.</t>
+          <t>UI + reliably persists local session (team details) so they appear in PatrolReportScreen; creates backend patrol at start.</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>End time + stats persisted on stop (ActivitySummary) and POSTed to /api/patrols/:id/complete; shown in PatrolReportScreen timing section.</t>
+          <t>End time + stats persisted on stop and POSTed to /api/patrols/:id/complete. End time now anchored to the real patrol stop time (trusted timer) instead of the last GPS sample, so duration reflects true start-&gt;end (fixes collapsed ~2-min durations). End Patrol button now hides immediately on confirm and navigation is not blocked by sync errors.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>PatrolReportScreen falls back to GET /api/patrols/:id (+stats) when no local session; renders summary/timing/team. Route map still local-only (no GET points endpoint).</t>
+          <t>Falls back to GET /api/patrols/:id when no local session; renders summary/timing/team. Team details + duration now correct (local session persistence + real end time fixed this session). Route map still local-only (no GET points endpoint).</t>
         </is>
       </c>
     </row>
@@ -2270,6 +2270,72 @@
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>Real-device forest test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>K01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Localization &amp; i18n</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>In-app language selector (Settings -&gt; Language)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Settings -&gt; Language offers English, Hindi, Telugu, Bengali; runtime locale switch via ContextWrapper; bottom-nav labels localized through nav_* string resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>K02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Localization &amp; i18n</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Translated string resources (hi/te/bn)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>70</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>nav_*, settings and core strings translated; full catalog coverage still pending.</t>
         </is>
       </c>
     </row>

--- a/docs/work_plan.xlsx
+++ b/docs/work_plan.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,30 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E4620"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2E7D32"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -69,8 +91,20 @@
         <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E4620"/>
+        <bgColor rgb="001E4620"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -92,11 +126,25 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -118,6 +166,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,1861 +548,294 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NSTR Patrol - Android App Work Plan (REAL STATUS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>NSTR Patrol - Android App Work Plan (Ansar Ali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Module / Area</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Sub-Item / Functionality</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Completion %</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Est. Remaining (hrs)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Notes / Remarks</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Build &amp; Config</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>AGP namespace + applicationId</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" s="3" t="n">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; 3D Visualization</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>3D Perspective View for Offline &amp; Online Maps</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Verified aligned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Build &amp; Config</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Centralized tunables (AppConfig)</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Enabled dynamic 3D camera pitch/perspective mode (58° tilt) with floating 2D/3D toggle across MBTiles offline raster and online basemaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; Basemaps</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>High-Resolution Google Satellite Hybrid Imagery</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>All consts in AppConfig.kt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Build &amp; Config</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Release signing + CI pipeline</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>release minify on; signing/CI not confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Build &amp; Config</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>API base URL build config</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Replaced low-resolution/error-prone Esri layers with Google Satellite Hybrid (z=0–21) and Google Terrain (z=0–20) for crisp deep zoom without missing data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; GIS Intelligence</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Forest Beat Boundary Grid Clipping</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>-PapiBaseUrl; default 10.0.2.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Auth &amp; Device</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Login (POST /api/auth/login)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Works.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Auth &amp; Device</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Auth session / token storage</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>AuthSession.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>B03</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Auth &amp; Device</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Device registration (POST /api/devices)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3" t="n">
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Spatial ray-casting algorithm confines dynamic km² grid meshes strictly to the 44 Markapur Forest Beat polygons with zero outer spillover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; Navigation</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Google Maps-Style 2-Finger Drag-to-Tilt 3D Gesture</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>On login.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>B04</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Auth &amp; Device</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Network client (no retry/timeout)</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>OkHttp exists; no resilience layer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>PatrolStartScreen UI</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>UI + reliably persists local session (team details) so they appear in PatrolReportScreen; creates backend patrol at start.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>PatrolTimer local elapsed clock</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F12" s="3" t="n">
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Multi-touch gesture handling on MapView smoothly tilts camera between 0° and 60° with synchronized 3D toggle state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; UI Controls</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Scrollable Map Layers Sheet &amp; Apply Button Fix</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>Local monotonic clock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>CREATE PATROL on backend</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Client-generated patrolId registered at start; PatrolStartScreen calls api.createPatrol; backend accepts client id (forestId resolved server-side). Requires &gt;=1 forest row in DB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Record patrol END TIME + status</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Added vertical scrolling to Map Layers bottom sheet, header close (X) icon, and prominent APPLY LAYERS button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Maps &amp; GIS Intelligence</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Automated Geodesic Polygon Area Calculation</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>End time + stats persisted on stop and POSTed to /api/patrols/:id/complete. End time now anchored to the real patrol stop time (trusted timer) instead of the last GPS sample, so duration reflects true start-&gt;end (fixes collapsed ~2-min durations). End Patrol button now hides immediately on confirm and navigation is not blocked by sync errors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>AllPatrolsScreen real data</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>AllPatrolsScreen now fetches GET /api/patrols (source of truth) and shows local PENDING sessions; static mock list removed. Dedupe via syncStatus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>C06</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>PatrolReportScreen (server report)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Falls back to GET /api/patrols/:id when no local session; renders summary/timing/team. Team details + duration now correct (local session persistence + real end time fixed this session). Route map still local-only (no GET points endpoint).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Patrol Lifecycle</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Server-side patrol tracking</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Depends on C03/C04+D07; backend tracking now reachable via sync upload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>GPS capture local</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>GpsTelemetryManager.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Persist patrol points locally (Room)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Every 30s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>D03</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Sensor readings local</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Recorded locally.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Movement classification</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>PatrolsAppScreen lists server patrols; PatrolReportScreen loads detail + stats + server route points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>D05</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Activity summary / metrics</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Local.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>D06</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Time integrity / tamper</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>TrustedTimeManager.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>D07</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>TELEMETRY SYNC UPLOAD</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>SyncManager.syncNow pushes PENDING patrol rows + points + readings via /api/sync/upload. Triggered on start, every 30s while running, and on stop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Offline sync queue / WorkManager</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Sync is mobile-&gt;server only, connectivity-driven: ConnectivityObserver fires SyncManager.syncNow on (re)connect plus on start/stop. No network/server polling. WorkManager background scheduled sync still TODO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Register server patrolId before sync</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>patrolId generated client-side at start and registered before tracking begins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Telemetry &amp; Tracking</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Live telemetry to server</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Server upload works when connectivity is gained (event-driven); not streamed continuously yet. Depends on D07 (done).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Offline MBTiles atlas + tile server</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Fetches from backend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>E02</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>GIS beats + compartments layers</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Real backend data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Incident / sighting markers</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>From GIS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Live patrol track (line + dots)</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Added this session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Satellite deep-zoom basemap</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Esri; maxZoom 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Layer controls + legend</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Fullscreen map mode</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>E08</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Maps</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Connect map track to live server</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>Local track already shown on map; now synced to server via D07.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Incident / Reporting</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Reporting screens UI</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Reporting screens (HumanImpact/AnimalMortality/Sighting/WaterSource/QuickCapture) now capture input and submit via submitIncident().</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>F02</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Incident / Reporting</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Incident + QuickCapture SYNC UPLOAD</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Local IncidentEntity + DAO + SyncManager.syncIncidents pushes pending incidents via /api/sync/upload (entity 'incidents'). All 5 reporting screens persist locally and sync on connectivity. Image upload (F04) still pending.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Incident / Reporting</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Image persistent storage w/ timestamp</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>MISSING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>F04</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Incident / Reporting</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Image upload API + send</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>No multipart upload in mobile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>F05</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Incident / Reporting</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Reports dynamic data + dropdown fixes</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>STATIC + dropdown bugs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>G01</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>SOS</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>SosScreen UI</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>UI exists; no POST.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>G02</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>SOS</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>SOS submit to backend</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>Backend ready; mobile never calls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>G03</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>SOS</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Emergency contacts fetch</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>MISSING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>G04</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>SOS</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Push notifications (FCM)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>PatrolReportScreen now draws route from server points for patrols recorded elsewhere (GET /api/patrols/:id/points).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>H01</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics &amp; Settings</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>GpsDiagnosticsScreen</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>Local.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>H02</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics &amp; Settings</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>SettingsScreen existing options</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>UI; wiring to verify.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>H03</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics &amp; Settings</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Settings functional options (offline map etc.)</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>MISSING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>H04</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics &amp; Settings</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>LogsScreen</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Local logs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>I01</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Navigation &amp; UX</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Bottom navigation</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>I02</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Navigation &amp; UX</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>ActivePatrolOverlay</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>I03</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Navigation &amp; UX</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>DASHBOARD real data (no pre-assigned)</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Rework needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>I04</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Navigation &amp; UX</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Theme / branding</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>Spot-check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>J01</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>QA &amp; Release</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>On-device build verification</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>compileDebugKotlin passing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>J02</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>QA &amp; Release</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>E2E patrol + sync test</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Blocked C03/D07.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>J03</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>QA &amp; Release</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Field / offline test</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Real-device forest test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>K01</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Localization &amp; i18n</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>In-app language selector (Settings -&gt; Language)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Settings -&gt; Language offers English, Hindi, Telugu, Bengali; runtime locale switch via ContextWrapper; bottom-nav labels localized through nav_* string resources.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>K02</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Localization &amp; i18n</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Translated string resources (hi/te/bn)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>70</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>nav_*, settings and core strings translated; full catalog coverage still pending.</t>
-        </is>
-      </c>
-    </row>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>WGS84 spherical geodesic polygon area engine for all 44 beats &amp; 448 compartments; fixed 0.00 ha bug (e.g. Magutur: 7,714.95 ha / 77.15 km²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1"/>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="20" customHeight="1"/>
+    <row r="17" ht="20" customHeight="1"/>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="27" ht="20" customHeight="1"/>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="33" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1"/>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1"/>
+    <row r="37" ht="20" customHeight="1"/>
+    <row r="38" ht="20" customHeight="1"/>
+    <row r="39" ht="20" customHeight="1"/>
+    <row r="40" ht="20" customHeight="1"/>
+    <row r="41" ht="20" customHeight="1"/>
+    <row r="42" ht="20" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A2:G55"/>
   <mergeCells count="1">
